--- a/data/out/variants/v3_no_solar_lags/summary_v3_no_solar_lags.xlsx
+++ b/data/out/variants/v3_no_solar_lags/summary_v3_no_solar_lags.xlsx
@@ -526,16 +526,16 @@
         <v>0.946583446936918</v>
       </c>
       <c r="F2" t="n">
-        <v>46.83099651102258</v>
+        <v>46.83099651102261</v>
       </c>
       <c r="G2" t="n">
-        <v>13429.85056728207</v>
+        <v>13429.85056728208</v>
       </c>
       <c r="H2" t="n">
         <v>115.8872321150267</v>
       </c>
       <c r="I2" t="n">
-        <v>11.52094070449527</v>
+        <v>11.52094070449531</v>
       </c>
       <c r="J2" t="n">
         <v>48168</v>
@@ -547,7 +547,7 @@
         <v>9634</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1193954944610596</v>
+        <v>0.1147961616516113</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.9465808168526716</v>
+        <v>0.9465808024459219</v>
       </c>
       <c r="F3" t="n">
-        <v>46.84315783661867</v>
+        <v>46.84317318214146</v>
       </c>
       <c r="G3" t="n">
-        <v>13430.51181620928</v>
+        <v>13430.51543831675</v>
       </c>
       <c r="H3" t="n">
-        <v>115.8900850642939</v>
+        <v>115.8901006916326</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5235131099911</v>
+        <v>11.52353008575009</v>
       </c>
       <c r="J3" t="n">
         <v>48168</v>
@@ -598,7 +598,7 @@
         <v>9634</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09428811073303223</v>
+        <v>0.08159112930297852</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.9467620754561299</v>
+        <v>0.9467562601333099</v>
       </c>
       <c r="F4" t="n">
-        <v>46.18826051122475</v>
+        <v>46.22910010956242</v>
       </c>
       <c r="G4" t="n">
-        <v>13384.94025048873</v>
+        <v>13386.40232379737</v>
       </c>
       <c r="H4" t="n">
-        <v>115.6933025308239</v>
+        <v>115.6996211048133</v>
       </c>
       <c r="I4" t="n">
-        <v>11.06744272409457</v>
+        <v>11.089619513876</v>
       </c>
       <c r="J4" t="n">
         <v>48168</v>
@@ -649,7 +649,7 @@
         <v>9634</v>
       </c>
       <c r="M4" t="n">
-        <v>4.111449956893921</v>
+        <v>4.514874935150146</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9464777576819509</v>
+        <v>0.9464759230207844</v>
       </c>
       <c r="F5" t="n">
-        <v>47.23368320928826</v>
+        <v>47.23632899789668</v>
       </c>
       <c r="G5" t="n">
-        <v>13456.42268433911</v>
+        <v>13456.88395006844</v>
       </c>
       <c r="H5" t="n">
-        <v>116.0018219009474</v>
+        <v>116.0038100670338</v>
       </c>
       <c r="I5" t="n">
-        <v>11.56559885659792</v>
+        <v>11.56804647756084</v>
       </c>
       <c r="J5" t="n">
         <v>48168</v>
@@ -704,7 +704,7 @@
         <v>9634</v>
       </c>
       <c r="M5" t="n">
-        <v>59.11264896392822</v>
+        <v>43.06809878349304</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-38.95632625345431</v>
+        <v>-38.95437003654128</v>
       </c>
     </row>
     <row r="6">
@@ -740,7 +740,7 @@
         <v>0.8414632613956308</v>
       </c>
       <c r="F6" t="n">
-        <v>74.49491854489351</v>
+        <v>74.49491854489344</v>
       </c>
       <c r="G6" t="n">
         <v>39858.89367227718</v>
@@ -749,7 +749,7 @@
         <v>199.6469225214283</v>
       </c>
       <c r="I6" t="n">
-        <v>11.67003922183375</v>
+        <v>11.67003922183372</v>
       </c>
       <c r="J6" t="n">
         <v>48168</v>
@@ -761,7 +761,7 @@
         <v>9634</v>
       </c>
       <c r="M6" t="n">
-        <v>11.12826251983643</v>
+        <v>9.718174695968628</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-73.29005104872532</v>
+        <v>-72.5177787057771</v>
       </c>
     </row>
     <row r="7">
@@ -790,23 +790,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 500}</t>
+          <t>{'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 500}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8158969581662386</v>
+        <v>0.8148690105119042</v>
       </c>
       <c r="F7" t="n">
-        <v>76.06626678687475</v>
+        <v>76.16172420029649</v>
       </c>
       <c r="G7" t="n">
-        <v>46286.70700428079</v>
+        <v>46545.15092469619</v>
       </c>
       <c r="H7" t="n">
-        <v>215.1434568009931</v>
+        <v>215.7432523271497</v>
       </c>
       <c r="I7" t="n">
-        <v>11.44827844170461</v>
+        <v>11.44813425816962</v>
       </c>
       <c r="J7" t="n">
         <v>48168</v>
@@ -818,7 +818,7 @@
         <v>9634</v>
       </c>
       <c r="M7" t="n">
-        <v>4810.316721439362</v>
+        <v>3044.743782758713</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-77.89237546824106</v>
+        <v>-77.78333237584279</v>
       </c>
     </row>
     <row r="8">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6867029867962866</v>
+        <v>0.6876443221920716</v>
       </c>
       <c r="F8" t="n">
-        <v>94.73942505100666</v>
+        <v>94.57685925806162</v>
       </c>
       <c r="G8" t="n">
-        <v>78768.31860589742</v>
+        <v>78531.65051381449</v>
       </c>
       <c r="H8" t="n">
-        <v>280.6569411325817</v>
+        <v>280.2349915942235</v>
       </c>
       <c r="I8" t="n">
-        <v>12.68952357186323</v>
+        <v>12.68479724990632</v>
       </c>
       <c r="J8" t="n">
         <v>48168</v>
@@ -875,7 +875,7 @@
         <v>9634</v>
       </c>
       <c r="M8" t="n">
-        <v>2095.289754390717</v>
+        <v>759.7761492729187</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-73.34040001700204</v>
+        <v>-74.74043585176777</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2483278618523376</v>
+        <v>0.2447152945338208</v>
       </c>
       <c r="F9" t="n">
-        <v>199.5419451268358</v>
+        <v>200.7809022165001</v>
       </c>
       <c r="G9" t="n">
-        <v>188983.4501112615</v>
+        <v>189891.7123721122</v>
       </c>
       <c r="H9" t="n">
-        <v>434.722267788598</v>
+        <v>435.7656622223833</v>
       </c>
       <c r="I9" t="n">
-        <v>42.39064248667367</v>
+        <v>42.71172137803913</v>
       </c>
       <c r="J9" t="n">
         <v>48168</v>
@@ -932,7 +932,7 @@
         <v>9634</v>
       </c>
       <c r="M9" t="n">
-        <v>885.4310867786407</v>
+        <v>264.7820379734039</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-206.2961122063612</v>
+        <v>-206.3839800008152</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6130833529823264</v>
+        <v>0.6114953191789452</v>
       </c>
       <c r="F10" t="n">
-        <v>151.2240938343367</v>
+        <v>153.0017685874433</v>
       </c>
       <c r="G10" t="n">
-        <v>97277.57508622311</v>
+        <v>97676.83440664419</v>
       </c>
       <c r="H10" t="n">
-        <v>311.8935316517852</v>
+        <v>312.5329333152655</v>
       </c>
       <c r="I10" t="n">
-        <v>38.31370113419317</v>
+        <v>38.37953217235387</v>
       </c>
       <c r="J10" t="n">
         <v>48168</v>
@@ -989,7 +989,7 @@
         <v>9634</v>
       </c>
       <c r="M10" t="n">
-        <v>10.67252111434937</v>
+        <v>2.611468315124512</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-119.0481183062341</v>
+        <v>-119.1727352926966</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 437, 'learning_rate': 0.03406029700907093, 'max_depth': 3, 'subsample': 0.9118101071407112, 'colsample_bytree': 0.8596265267479997}</t>
+          <t>{'n_estimators': 273, 'learning_rate': 0.049124815068632345, 'max_depth': 3, 'subsample': 0.8300775351338086, 'colsample_bytree': 0.8593409700311154}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8096174793052274</v>
+        <v>0.8108139358251421</v>
       </c>
       <c r="F11" t="n">
-        <v>78.75639540811879</v>
+        <v>78.76945977617849</v>
       </c>
       <c r="G11" t="n">
-        <v>47865.47721515898</v>
+        <v>47564.66723489445</v>
       </c>
       <c r="H11" t="n">
-        <v>218.7818027514148</v>
+        <v>218.0932535290683</v>
       </c>
       <c r="I11" t="n">
-        <v>11.94588677750293</v>
+        <v>11.92985558859592</v>
       </c>
       <c r="J11" t="n">
         <v>48168</v>
@@ -1046,7 +1046,7 @@
         <v>9634</v>
       </c>
       <c r="M11" t="n">
-        <v>303.6565661430359</v>
+        <v>111.2319514751434</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 704, 'learning_rate': 0.013125275297510727, 'num_leaves': 31, 'min_child_samples': 19}</t>
+          <t>{'n_estimators': 523, 'learning_rate': 0.014125835558521002, 'num_leaves': 70, 'min_child_samples': 50}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7961007033398035</v>
+        <v>0.8082534758821526</v>
       </c>
       <c r="F12" t="n">
-        <v>80.32989067621897</v>
+        <v>78.9335666638603</v>
       </c>
       <c r="G12" t="n">
-        <v>51263.8298035916</v>
+        <v>48208.41140118786</v>
       </c>
       <c r="H12" t="n">
-        <v>226.4151713193964</v>
+        <v>219.564139606603</v>
       </c>
       <c r="I12" t="n">
-        <v>11.29530339703793</v>
+        <v>11.15584899882263</v>
       </c>
       <c r="J12" t="n">
         <v>48168</v>
@@ -1101,7 +1101,7 @@
         <v>9634</v>
       </c>
       <c r="M12" t="n">
-        <v>1495.618865728378</v>
+        <v>191.8904378414154</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 986, 'learning_rate': 0.010711756187326775, 'depth': 4}</t>
+          <t>{'iterations': 671, 'learning_rate': 0.014076614921829081, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8092292328583157</v>
+        <v>0.809814910830438</v>
       </c>
       <c r="F13" t="n">
-        <v>80.36283046872641</v>
+        <v>80.16853547694924</v>
       </c>
       <c r="G13" t="n">
-        <v>47963.08912506909</v>
+        <v>47815.83949559821</v>
       </c>
       <c r="H13" t="n">
-        <v>219.0047696399992</v>
+        <v>218.6683321736328</v>
       </c>
       <c r="I13" t="n">
-        <v>12.43914407011411</v>
+        <v>12.42682107406195</v>
       </c>
       <c r="J13" t="n">
         <v>48168</v>
@@ -1156,7 +1156,7 @@
         <v>9634</v>
       </c>
       <c r="M13" t="n">
-        <v>685.5878901481628</v>
+        <v>179.8541188240051</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 20, 'min_samples_split': 2, 'n_estimators': 300}</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 500}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7326333419522457</v>
+        <v>0.7159752391479505</v>
       </c>
       <c r="F14" t="n">
-        <v>92.05000005585892</v>
+        <v>91.88854747219007</v>
       </c>
       <c r="G14" t="n">
-        <v>67220.62840735029</v>
+        <v>71408.76520329651</v>
       </c>
       <c r="H14" t="n">
-        <v>259.2694127878379</v>
+        <v>267.2241852888629</v>
       </c>
       <c r="I14" t="n">
-        <v>13.52484285961132</v>
+        <v>12.22675267955884</v>
       </c>
       <c r="J14" t="n">
         <v>48168</v>
@@ -1211,7 +1211,7 @@
         <v>9634</v>
       </c>
       <c r="M14" t="n">
-        <v>774.1128458976746</v>
+        <v>184.6192047595978</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-72.34503672232356</v>
+        <v>-72.19968757145718</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9634</v>
       </c>
       <c r="M15" t="n">
-        <v>76.98302817344666</v>
+        <v>20.57431030273438</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1301,19 +1301,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9266223928656123</v>
+        <v>0.9383329272462376</v>
       </c>
       <c r="F16" t="n">
-        <v>58.52712782732951</v>
+        <v>54.4718350350253</v>
       </c>
       <c r="G16" t="n">
-        <v>18448.40676327045</v>
+        <v>15504.17472701216</v>
       </c>
       <c r="H16" t="n">
-        <v>135.8249121599954</v>
+        <v>124.5157609582504</v>
       </c>
       <c r="I16" t="n">
-        <v>12.25684443501918</v>
+        <v>13.11534148037239</v>
       </c>
       <c r="J16" t="n">
         <v>48168</v>
@@ -1325,7 +1325,7 @@
         <v>9634</v>
       </c>
       <c r="M16" t="n">
-        <v>2225.826884269714</v>
+        <v>1907.474280595779</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-40.50466351791096</v>
+        <v>-39.68060711986657</v>
       </c>
     </row>
   </sheetData>
